--- a/clinic_bonus_template.xlsx
+++ b/clinic_bonus_template.xlsx
@@ -776,7 +776,7 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>代謝症候群：收案 100 元/筆、追蹤 20 元/筆，給該筆執行員工。</t>
+          <t>代謝症候群：收案 100 元/筆、追蹤 20 元/筆，給該筆執行人員。</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="E1" s="5" t="inlineStr">
         <is>
-          <t>執行員工</t>
+          <t>執行人員</t>
         </is>
       </c>
       <c r="F1" s="5" t="inlineStr">

--- a/clinic_bonus_template.xlsx
+++ b/clinic_bonus_template.xlsx
@@ -1339,7 +1339,7 @@
       </c>
       <c r="F1" s="5" t="inlineStr">
         <is>
-          <t>患者代號</t>
+          <t>病歷號</t>
         </is>
       </c>
       <c r="G1" s="5" t="inlineStr">

--- a/clinic_bonus_template.xlsx
+++ b/clinic_bonus_template.xlsx
@@ -1360,7 +1360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1371,6 +1371,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1412,6 +1413,11 @@
       <c r="H1" s="5" t="inlineStr">
         <is>
           <t>流感支數</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>病歷號</t>
         </is>
       </c>
     </row>

--- a/clinic_bonus_template.xlsx
+++ b/clinic_bonus_template.xlsx
@@ -117,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -140,6 +140,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -299,7 +303,7 @@
   <commentList>
     <comment ref="H2" authorId="0" shapeId="0">
       <text>
-        <t>輸入欲查詢的年月（格式：YYYY-MM）。修改後 I 欄表格會自動更新。</t>
+        <t>從下拉選單選擇要查詢的年月。修改後右側 I 欄表格會自動更新。</t>
       </text>
     </comment>
   </commentList>
@@ -1433,7 +1437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:V84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1451,6 +1455,7 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
+    <col hidden="1" width="12" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1479,6 +1484,11 @@
           <t>區塊 4：本月診次彙總（cross-check 帳本）</t>
         </is>
       </c>
+      <c r="V1" s="12" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -1489,19 +1499,143 @@
         <f>QUERY('分紅明細'!B:F,"SELECT D, E, SUM(F) WHERE B &gt;= date '"&amp;TEXT(EOMONTH(TODAY(),-1)+1,"yyyy-MM-dd")&amp;"' AND B &lt;= date '"&amp;TEXT(EOMONTH(TODAY(),0),"yyyy-MM-dd")&amp;"' GROUP BY D, E ORDER BY D, E LABEL SUM(F) '小計'", 1)</f>
         <v/>
       </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>2026-04</t>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="I2">
-        <f>QUERY('分紅明細'!B:F,"SELECT D, SUM(F) WHERE B &gt;= date '"&amp;H2&amp;"-01' AND B &lt;= date '"&amp;TEXT(EOMONTH(DATEVALUE(H2&amp;"-01"),0),"yyyy-MM-dd")&amp;"' GROUP BY D ORDER BY SUM(F) DESC LABEL SUM(F) 'TARGET月總分紅'", 1)</f>
+        <f>QUERY('分紅明細'!B:F,"SELECT D, SUM(F) WHERE B &gt;= date '"&amp;LEFT(H2,7)&amp;"-01' AND B &lt;= date '"&amp;TEXT(EOMONTH(DATEVALUE(LEFT(H2,7)&amp;"-01"),0),"yyyy-MM-dd")&amp;"' GROUP BY D ORDER BY SUM(F) DESC LABEL SUM(F) '查詢月總分紅'", 1)</f>
         <v/>
       </c>
       <c r="L2">
         <f>QUERY('Form回應_當班'!A:J,"SELECT B, C, H, I WHERE B &gt;= date '"&amp;TEXT(EOMONTH(TODAY(),-1)+1,"yyyy-MM-dd")&amp;"' AND B &lt;= date '"&amp;TEXT(EOMONTH(TODAY(),0),"yyyy-MM-dd")&amp;"' ORDER BY B, C LABEL B '日期', C '時段', H '看診人數', I '流感支數'", 1)</f>
         <v/>
       </c>
+      <c r="V2" s="12" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="V3" s="12" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="V4" s="12" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="V5" s="12" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="V6" s="12" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="V7" s="12" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="V8" s="12" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="V9" s="12" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="V10" s="12" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="V11" s="12" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="V12" s="12" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="V13" s="12" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="V14" s="12" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="V15" s="12" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="V16" s="12" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="V17" s="12" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="V18" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="V19" s="12" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
@@ -1509,6 +1643,11 @@
           <t>※ 使用說明</t>
         </is>
       </c>
+      <c r="V20" s="12" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1516,6 +1655,11 @@
           <t>1) 此 .xlsx 上傳 Google Drive → 右鍵「以 Google 試算表開啟」後，所有 QUERY 公式才會運作。</t>
         </is>
       </c>
+      <c r="V21" s="12" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1523,6 +1667,11 @@
           <t>2) 本機 Excel 不支援 QUERY()，請忽略 #NAME? 錯誤，以 Sheets 為準。</t>
         </is>
       </c>
+      <c r="V22" s="12" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1530,6 +1679,11 @@
           <t>3) 區塊 1、2、4 自動抓「本月」，月初自動切換。</t>
         </is>
       </c>
+      <c r="V23" s="12" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1537,11 +1691,434 @@
           <t>4) 區塊 3 修改 H2 年月即可查詢任意月份。</t>
         </is>
       </c>
+      <c r="V24" s="12" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
           <t>5) 員工嚴禁存取此檔案；僅 owner（徐醫師）+ 主任（editor）有權限。</t>
+        </is>
+      </c>
+      <c r="V25" s="12" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="V26" s="12" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="V27" s="12" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="V28" s="12" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="V29" s="12" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="V30" s="12" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="V31" s="12" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="V32" s="12" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="V33" s="12" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="V34" s="12" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="V35" s="12" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="V36" s="12" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="V37" s="12" t="inlineStr">
+        <is>
+          <t>2027-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="V38" s="12" t="inlineStr">
+        <is>
+          <t>2027-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="V39" s="12" t="inlineStr">
+        <is>
+          <t>2027-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="V40" s="12" t="inlineStr">
+        <is>
+          <t>2027-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="V41" s="12" t="inlineStr">
+        <is>
+          <t>2027-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="V42" s="12" t="inlineStr">
+        <is>
+          <t>2027-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="V43" s="12" t="inlineStr">
+        <is>
+          <t>2027-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="V44" s="12" t="inlineStr">
+        <is>
+          <t>2027-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="V45" s="12" t="inlineStr">
+        <is>
+          <t>2027-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="V46" s="12" t="inlineStr">
+        <is>
+          <t>2027-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="V47" s="12" t="inlineStr">
+        <is>
+          <t>2027-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="V48" s="12" t="inlineStr">
+        <is>
+          <t>2027-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="V49" s="12" t="inlineStr">
+        <is>
+          <t>2028-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="V50" s="12" t="inlineStr">
+        <is>
+          <t>2028-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="V51" s="12" t="inlineStr">
+        <is>
+          <t>2028-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="V52" s="12" t="inlineStr">
+        <is>
+          <t>2028-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="V53" s="12" t="inlineStr">
+        <is>
+          <t>2028-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="V54" s="12" t="inlineStr">
+        <is>
+          <t>2028-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="V55" s="12" t="inlineStr">
+        <is>
+          <t>2028-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="V56" s="12" t="inlineStr">
+        <is>
+          <t>2028-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="V57" s="12" t="inlineStr">
+        <is>
+          <t>2028-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="V58" s="12" t="inlineStr">
+        <is>
+          <t>2028-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="V59" s="12" t="inlineStr">
+        <is>
+          <t>2028-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="V60" s="12" t="inlineStr">
+        <is>
+          <t>2028-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="V61" s="12" t="inlineStr">
+        <is>
+          <t>2029-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="V62" s="12" t="inlineStr">
+        <is>
+          <t>2029-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="V63" s="12" t="inlineStr">
+        <is>
+          <t>2029-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="V64" s="12" t="inlineStr">
+        <is>
+          <t>2029-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="V65" s="12" t="inlineStr">
+        <is>
+          <t>2029-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="V66" s="12" t="inlineStr">
+        <is>
+          <t>2029-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="V67" s="12" t="inlineStr">
+        <is>
+          <t>2029-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="V68" s="12" t="inlineStr">
+        <is>
+          <t>2029-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="V69" s="12" t="inlineStr">
+        <is>
+          <t>2029-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="V70" s="12" t="inlineStr">
+        <is>
+          <t>2029-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="V71" s="12" t="inlineStr">
+        <is>
+          <t>2029-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="V72" s="12" t="inlineStr">
+        <is>
+          <t>2029-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="V73" s="12" t="inlineStr">
+        <is>
+          <t>2030-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="V74" s="12" t="inlineStr">
+        <is>
+          <t>2030-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="V75" s="12" t="inlineStr">
+        <is>
+          <t>2030-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="V76" s="12" t="inlineStr">
+        <is>
+          <t>2030-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="V77" s="12" t="inlineStr">
+        <is>
+          <t>2030-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="V78" s="12" t="inlineStr">
+        <is>
+          <t>2030-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="V79" s="12" t="inlineStr">
+        <is>
+          <t>2030-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="V80" s="12" t="inlineStr">
+        <is>
+          <t>2030-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="V81" s="12" t="inlineStr">
+        <is>
+          <t>2030-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="V82" s="12" t="inlineStr">
+        <is>
+          <t>2030-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="V83" s="12" t="inlineStr">
+        <is>
+          <t>2030-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="V84" s="12" t="inlineStr">
+        <is>
+          <t>2030-12</t>
         </is>
       </c>
     </row>
@@ -1557,6 +2134,11 @@
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="A23:G23"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="H2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="無效年月" error="請從下拉選單選擇年月" promptTitle="查詢年月" prompt="點此選擇要查詢的年月" type="list">
+      <formula1>=$V$1:$V$84</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>

--- a/clinic_bonus_template.xlsx
+++ b/clinic_bonus_template.xlsx
@@ -599,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -766,82 +766,89 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>基礎分紅 = MAX(0, 看診 - 流感 - 60) × 5 + 流感 × 5（每位當班員工平均分）。</t>
+          <t>基礎分紅 = MAX(0, 看診 - 流感 - 評估 - 60) × 5 + 流感 × 5 + 評估 × 5。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>值日生津貼 = 100 元（僅上午/下午、值日生一人）。</t>
+          <t>（評估 = Peak flow/ACT/POEM，一位病人一次算 1 筆；每位當班員工平均分）</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>代謝症候群：收案 100 元/筆、追蹤 20 元/筆，給該筆執行人員。</t>
+          <t>值日生津貼 = 100 元（僅上午/下午、值日生一人）。</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
+          <t>代謝症候群：收案 100 元/筆、追蹤 20 元/筆，給該筆執行人員。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
           <t>詳見 README.md 與 apps_script.gs。</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>六、分頁清單</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>1. 員工總表（唯一手動維護處）</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2. 單價參數</t>
+          <t>1. 員工總表（唯一手動維護處）</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>3. Form回應_當班（Form 1 自動寫入）</t>
+          <t>2. 單價參數</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>4. Form回應_代謝（Form 2 自動寫入）</t>
+          <t>3. Form回應_當班（Form 1 自動寫入）</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>5. 分紅明細（Apps Script 自動 append，月結算來源）</t>
+          <t>4. Form回應_代謝（Form 2 自動寫入）</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
+          <t>5. 分紅明細（Apps Script 自動 append，月結算來源）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
           <t>6. 月度結算（含 QUERY 公式，上傳 Sheets 後生效）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="34">
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="A34:E34"/>
@@ -859,9 +866,9 @@
     <mergeCell ref="A27:E27"/>
     <mergeCell ref="A12:E12"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A33:E33"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A32:E32"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A29:E29"/>
@@ -874,6 +881,7 @@
     <mergeCell ref="A19:E19"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A40:E40"/>
     <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1187,13 +1195,28 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
+          <t>氣喘/濕疹評估單價</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Peak flow/ACT/POEM 每筆 5 元，一位病人一次門診算 1 筆</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
           <t>值日生人數門檻</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>（目前未使用，預留）</t>
         </is>
@@ -1224,7 +1247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1236,7 +1259,8 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1286,6 +1310,11 @@
         </is>
       </c>
       <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>氣喘/濕疹評估筆數</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
@@ -1364,7 +1393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1376,6 +1405,7 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1422,6 +1452,11 @@
       <c r="I1" s="5" t="inlineStr">
         <is>
           <t>病歷號</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>評估筆數</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1544,7 @@
         <v/>
       </c>
       <c r="L2">
-        <f>QUERY('Form回應_當班'!A:J,"SELECT B, C, H, I WHERE B &gt;= date '"&amp;TEXT(EOMONTH(TODAY(),-1)+1,"yyyy-MM-dd")&amp;"' AND B &lt;= date '"&amp;TEXT(EOMONTH(TODAY(),0),"yyyy-MM-dd")&amp;"' ORDER BY B, C LABEL B '日期', C '時段', H '看診人數', I '流感支數'", 1)</f>
+        <f>QUERY('Form回應_當班'!A:K,"SELECT B, C, H, I, J WHERE B &gt;= date '"&amp;TEXT(EOMONTH(TODAY(),-1)+1,"yyyy-MM-dd")&amp;"' AND B &lt;= date '"&amp;TEXT(EOMONTH(TODAY(),0),"yyyy-MM-dd")&amp;"' ORDER BY B, C LABEL B '日期', C '時段', H '看診人數', I '流感支數', J '評估筆數'", 1)</f>
         <v/>
       </c>
       <c r="V2" s="12" t="inlineStr">

--- a/clinic_bonus_template.xlsx
+++ b/clinic_bonus_template.xlsx
@@ -599,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -787,71 +787,77 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>代謝症候群：收案 100 元/筆、追蹤 20 元/筆，給該筆執行人員。</t>
+          <t>代謝症候群：收案(P7501) 100 元/筆、追蹤(P7502) 20 元/筆、</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
+          <t>年度評估(P7503) 20 元/筆，給該筆執行人員。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
           <t>詳見 README.md 與 apps_script.gs。</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>六、分頁清單</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>1. 員工總表（唯一手動維護處）</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2. 單價參數</t>
+          <t>1. 員工總表（唯一手動維護處）</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>3. Form回應_當班（Form 1 自動寫入）</t>
+          <t>2. 單價參數</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>4. Form回應_代謝（Form 2 自動寫入）</t>
+          <t>3. Form回應_當班（Form 1 自動寫入）</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>5. 分紅明細（Apps Script 自動 append，月結算來源）</t>
+          <t>4. Form回應_代謝（Form 2 自動寫入）</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
+          <t>5. 分紅明細（Apps Script 自動 append，月結算來源）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
           <t>6. 月度結算（含 QUERY 公式，上傳 Sheets 後生效）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="34">
+  <mergeCells count="35">
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A34:E34"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="A11:E11"/>
@@ -861,11 +867,13 @@
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A7:E7"/>
     <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A41:E41"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="A18:E18"/>
     <mergeCell ref="A27:E27"/>
     <mergeCell ref="A12:E12"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A33:E33"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A32:E32"/>
@@ -1158,7 +1166,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>每筆 100 元</t>
+          <t>P7501，每筆 100 元</t>
         </is>
       </c>
     </row>
@@ -1173,50 +1181,65 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>每筆 20 元</t>
+          <t>P7502，每筆 20 元</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>值日生津貼</t>
+          <t>代謝症候群-年度評估</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>每時段 100 元</t>
+          <t>P7503，每筆 20 元</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>氣喘/濕疹評估單價</t>
+          <t>值日生津貼</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Peak flow/ACT/POEM 每筆 5 元，一位病人一次門診算 1 筆</t>
+          <t>每時段 100 元</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
+          <t>氣喘/濕疹評估單價</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Peak flow/ACT/POEM 每筆 5 元，一位病人一次門診算 1 筆</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
           <t>值日生人數門檻</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B10" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>（目前未使用，預留）</t>
         </is>
